--- a/input/timetable/Реклама и связи с общественностью.xlsx
+++ b/input/timetable/Реклама и связи с общественностью.xlsx
@@ -347,9 +347,6 @@
     <t>Психология (лек)/(пр), Г306</t>
   </si>
   <si>
-    <t>Основы проектирования в профессиональной деятельности (пр), ЭОиДОТ</t>
-  </si>
-  <si>
     <t>Основы проектирования в профессиональной деятельности (лек), Г305</t>
   </si>
   <si>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>Пресс-служба (пр), Г319</t>
+  </si>
+  <si>
+    <t>Основы проектирования в профессиональной деятельности (пр), Г305</t>
   </si>
 </sst>
 </file>
@@ -1599,15 +1599,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1714,6 +1705,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2817,12 +2817,12 @@
       <c r="B13" s="35">
         <v>5</v>
       </c>
-      <c r="C13" s="179" t="s">
+      <c r="C13" s="176" t="s">
         <v>81</v>
       </c>
       <c r="D13" s="162"/>
-      <c r="E13" s="180"/>
-      <c r="F13" s="181"/>
+      <c r="E13" s="177"/>
+      <c r="F13" s="178"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="26"/>
@@ -2916,7 +2916,7 @@
       <c r="E21" s="125"/>
       <c r="F21" s="126"/>
     </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="30"/>
       <c r="B22" s="27">
         <v>4</v>
@@ -2945,19 +2945,17 @@
       <c r="B24" s="25">
         <v>4</v>
       </c>
-      <c r="C24" s="164"/>
-      <c r="D24" s="165"/>
-      <c r="E24" s="165"/>
-      <c r="F24" s="166"/>
-    </row>
-    <row r="25" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C24" s="150"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="152"/>
+    </row>
+    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="46"/>
       <c r="B25" s="35">
         <v>5</v>
       </c>
-      <c r="C25" s="156" t="s">
-        <v>107</v>
-      </c>
+      <c r="C25" s="156"/>
       <c r="D25" s="157"/>
       <c r="E25" s="157"/>
       <c r="F25" s="158"/>
@@ -2967,10 +2965,10 @@
       <c r="B26" s="27">
         <v>6</v>
       </c>
-      <c r="C26" s="173"/>
-      <c r="D26" s="174"/>
-      <c r="E26" s="174"/>
-      <c r="F26" s="175"/>
+      <c r="C26" s="170"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="172"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="28" t="s">
@@ -2979,10 +2977,10 @@
       <c r="B27" s="29">
         <v>3</v>
       </c>
-      <c r="C27" s="176"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="177"/>
-      <c r="F27" s="178"/>
+      <c r="C27" s="173"/>
+      <c r="D27" s="174"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="175"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="31"/>
@@ -3028,7 +3026,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D31" s="89"/>
       <c r="E31" s="89"/>
@@ -3040,7 +3038,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="150" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D32" s="151"/>
       <c r="E32" s="151"/>
@@ -3051,7 +3049,9 @@
       <c r="B33" s="27">
         <v>3</v>
       </c>
-      <c r="C33" s="95"/>
+      <c r="C33" s="95" t="s">
+        <v>111</v>
+      </c>
       <c r="D33" s="96"/>
       <c r="E33" s="96"/>
       <c r="F33" s="97"/>
@@ -3059,10 +3059,10 @@
     <row r="34" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="50"/>
       <c r="B34" s="51"/>
-      <c r="C34" s="167"/>
-      <c r="D34" s="168"/>
-      <c r="E34" s="168"/>
-      <c r="F34" s="169"/>
+      <c r="C34" s="164"/>
+      <c r="D34" s="165"/>
+      <c r="E34" s="165"/>
+      <c r="F34" s="166"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="52"/>
@@ -3093,12 +3093,12 @@
       <c r="B37" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="170" t="s">
+      <c r="C37" s="167" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="171"/>
-      <c r="E37" s="171"/>
-      <c r="F37" s="172"/>
+      <c r="D37" s="168"/>
+      <c r="E37" s="168"/>
+      <c r="F37" s="169"/>
     </row>
     <row r="38" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="57" t="s">
@@ -3384,12 +3384,12 @@
       <c r="B14" s="27">
         <v>6</v>
       </c>
-      <c r="C14" s="204" t="s">
+      <c r="C14" s="201" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
-      <c r="F14" s="206"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="203"/>
     </row>
     <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="28" t="s">
@@ -3399,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" s="116"/>
       <c r="E15" s="116"/>
@@ -3411,7 +3411,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D16" s="84"/>
       <c r="E16" s="84"/>
@@ -3425,17 +3425,17 @@
       <c r="C17" s="160"/>
       <c r="D17" s="161"/>
       <c r="E17" s="161"/>
-      <c r="F17" s="207"/>
+      <c r="F17" s="204"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="30"/>
       <c r="B18" s="27">
         <v>4</v>
       </c>
-      <c r="C18" s="201"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="202"/>
-      <c r="F18" s="203"/>
+      <c r="C18" s="198"/>
+      <c r="D18" s="199"/>
+      <c r="E18" s="199"/>
+      <c r="F18" s="200"/>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="28" t="s">
@@ -3444,12 +3444,12 @@
       <c r="B19" s="29">
         <v>1</v>
       </c>
-      <c r="C19" s="208" t="s">
+      <c r="C19" s="205" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="209"/>
-      <c r="E19" s="209"/>
-      <c r="F19" s="210"/>
+      <c r="D19" s="206"/>
+      <c r="E19" s="206"/>
+      <c r="F19" s="207"/>
     </row>
     <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
@@ -3468,24 +3468,24 @@
       <c r="B21" s="25">
         <v>3</v>
       </c>
-      <c r="C21" s="188" t="s">
+      <c r="C21" s="185" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="189"/>
-      <c r="E21" s="189"/>
-      <c r="F21" s="190"/>
+      <c r="D21" s="186"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="187"/>
     </row>
     <row r="22" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="30"/>
       <c r="B22" s="27">
         <v>4</v>
       </c>
-      <c r="C22" s="211"/>
-      <c r="D22" s="212"/>
-      <c r="E22" s="195" t="s">
+      <c r="C22" s="208"/>
+      <c r="D22" s="209"/>
+      <c r="E22" s="192" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="196"/>
+      <c r="F22" s="193"/>
     </row>
     <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="28" t="s">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D23" s="92"/>
       <c r="E23" s="92"/>
-      <c r="F23" s="194"/>
+      <c r="F23" s="191"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="24"/>
@@ -3518,7 +3518,7 @@
       <c r="B25" s="25">
         <v>3</v>
       </c>
-      <c r="C25" s="179" t="s">
+      <c r="C25" s="176" t="s">
         <v>59</v>
       </c>
       <c r="D25" s="162"/>
@@ -3530,12 +3530,12 @@
       <c r="B26" s="27">
         <v>4</v>
       </c>
-      <c r="C26" s="197" t="s">
+      <c r="C26" s="194" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="198"/>
-      <c r="E26" s="199"/>
-      <c r="F26" s="200"/>
+      <c r="D26" s="195"/>
+      <c r="E26" s="196"/>
+      <c r="F26" s="197"/>
     </row>
     <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="28" t="s">
@@ -3544,12 +3544,12 @@
       <c r="B27" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="191" t="s">
+      <c r="C27" s="188" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="192"/>
-      <c r="E27" s="192"/>
-      <c r="F27" s="193"/>
+      <c r="D27" s="189"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="190"/>
     </row>
     <row r="28" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31"/>
@@ -3580,10 +3580,10 @@
       <c r="B30" s="27">
         <v>6</v>
       </c>
-      <c r="C30" s="185"/>
-      <c r="D30" s="186"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="187"/>
+      <c r="C30" s="182"/>
+      <c r="D30" s="183"/>
+      <c r="E30" s="183"/>
+      <c r="F30" s="184"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="33" t="s">
@@ -3604,20 +3604,20 @@
       <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C32" s="182"/>
-      <c r="D32" s="183"/>
-      <c r="E32" s="183"/>
-      <c r="F32" s="184"/>
+      <c r="C32" s="179"/>
+      <c r="D32" s="180"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="181"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="48"/>
       <c r="B33" s="25">
         <v>4</v>
       </c>
-      <c r="C33" s="182"/>
-      <c r="D33" s="183"/>
-      <c r="E33" s="183"/>
-      <c r="F33" s="184"/>
+      <c r="C33" s="179"/>
+      <c r="D33" s="180"/>
+      <c r="E33" s="180"/>
+      <c r="F33" s="181"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="53"/>
@@ -3898,10 +3898,10 @@
       <c r="B13" s="25">
         <v>7</v>
       </c>
-      <c r="C13" s="164"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165"/>
-      <c r="F13" s="166"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="211"/>
+      <c r="E13" s="211"/>
+      <c r="F13" s="212"/>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="26"/>
@@ -3954,10 +3954,10 @@
       <c r="B18" s="27">
         <v>6</v>
       </c>
-      <c r="C18" s="173"/>
-      <c r="D18" s="174"/>
-      <c r="E18" s="174"/>
-      <c r="F18" s="175"/>
+      <c r="C18" s="170"/>
+      <c r="D18" s="171"/>
+      <c r="E18" s="171"/>
+      <c r="F18" s="172"/>
     </row>
     <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="28" t="s">
@@ -3990,10 +3990,10 @@
       <c r="B21" s="25">
         <v>4</v>
       </c>
-      <c r="C21" s="164"/>
-      <c r="D21" s="165"/>
-      <c r="E21" s="165"/>
-      <c r="F21" s="166"/>
+      <c r="C21" s="210"/>
+      <c r="D21" s="211"/>
+      <c r="E21" s="211"/>
+      <c r="F21" s="212"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="30"/>
@@ -4087,9 +4087,9 @@
         <v>3</v>
       </c>
       <c r="C29" s="219"/>
-      <c r="D29" s="180"/>
-      <c r="E29" s="180"/>
-      <c r="F29" s="181"/>
+      <c r="D29" s="177"/>
+      <c r="E29" s="177"/>
+      <c r="F29" s="178"/>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="32"/>
@@ -4120,20 +4120,20 @@
       <c r="B32" s="25">
         <v>2</v>
       </c>
-      <c r="C32" s="164"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="166"/>
+      <c r="C32" s="210"/>
+      <c r="D32" s="211"/>
+      <c r="E32" s="211"/>
+      <c r="F32" s="212"/>
     </row>
     <row r="33" spans="1:6" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="48"/>
       <c r="B33" s="25">
         <v>3</v>
       </c>
-      <c r="C33" s="164"/>
-      <c r="D33" s="165"/>
-      <c r="E33" s="165"/>
-      <c r="F33" s="166"/>
+      <c r="C33" s="210"/>
+      <c r="D33" s="211"/>
+      <c r="E33" s="211"/>
+      <c r="F33" s="212"/>
     </row>
     <row r="34" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="53"/>

--- a/input/timetable/Реклама и связи с общественностью.xlsx
+++ b/input/timetable/Реклама и связи с общественностью.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28470" windowHeight="14040" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28470" windowHeight="14040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <definedName name="Группы">#REF!</definedName>
     <definedName name="Подписи">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="135">
   <si>
     <t>пара</t>
   </si>
@@ -77,6 +77,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -134,6 +137,18 @@
     <t>Русский язык и культура речи (лек 32 ч)</t>
   </si>
   <si>
+    <t>Хадынская А.А.</t>
+  </si>
+  <si>
+    <t>Ганеева Л.Д.</t>
+  </si>
+  <si>
+    <t>Шевкунов А.Н.</t>
+  </si>
+  <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
     <t>Основы теории коммуникации (лек), Г212</t>
   </si>
   <si>
@@ -146,21 +161,42 @@
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Плеханова Н.П.</t>
+  </si>
+  <si>
+    <t>Назаров П.В.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
     <t>Учебная практика, профессионально-ознакомительная практика (бизнес-планирование), Г212</t>
   </si>
   <si>
+    <t>Вишнягова Е.П.</t>
+  </si>
+  <si>
     <t>213-31</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
+    <t>Шубина О.А.</t>
+  </si>
+  <si>
     <t>История России (лек 32 ч)</t>
   </si>
   <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (лек 16 ч)</t>
   </si>
   <si>
+    <t>Дроздова А.А.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (пр), К433</t>
   </si>
   <si>
@@ -188,6 +224,9 @@
     <t>Теория и практика массовой информации (лек)/(пр), Г212</t>
   </si>
   <si>
+    <t>Иванова О.А.</t>
+  </si>
+  <si>
     <t>Учебная практика, профессионально-ознакомительная практика (бизнес-планирование), Г212//</t>
   </si>
   <si>
@@ -212,6 +251,12 @@
     <t>Иностранный язык в проф. сфере (24 ч), п/г 1, Г224</t>
   </si>
   <si>
+    <t>Бебех В.А.</t>
+  </si>
+  <si>
+    <t>Богдан Е.С.</t>
+  </si>
+  <si>
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
@@ -242,15 +287,30 @@
     <t>02.02.2026-08.04.2026</t>
   </si>
   <si>
+    <t>Гузич М.Э.</t>
+  </si>
+  <si>
     <t>213-41</t>
   </si>
   <si>
+    <t>Викулов Е.А.</t>
+  </si>
+  <si>
+    <t>Воробьева А.Д.</t>
+  </si>
+  <si>
     <t>//Социология (лек), К426</t>
   </si>
   <si>
     <t>Социология (пр), К426</t>
   </si>
   <si>
+    <t>Подлуцкая К.А.</t>
+  </si>
+  <si>
+    <t>Гришенкова Т.Ф</t>
+  </si>
+  <si>
     <t>Мировой опыт художественной культуры в рекламе и связях с общественностью (лек)/(пр), К413</t>
   </si>
   <si>
@@ -269,6 +329,15 @@
     <t>Иностранный язык, п/г 2, К409</t>
   </si>
   <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
+    <t>Плесовских И.Н./Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Афян К.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 1, К413</t>
   </si>
   <si>
@@ -284,9 +353,6 @@
     <t>Основы маркетинга (лек), К427</t>
   </si>
   <si>
-    <t>Основы маркетинга (пр), К518</t>
-  </si>
-  <si>
     <t>Элективные дисциплины по физической культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины</t>
   </si>
   <si>
@@ -360,6 +426,9 @@
   </si>
   <si>
     <t>Основы проектирования в профессиональной деятельности (пр), Г305</t>
+  </si>
+  <si>
+    <t>Основы маркетинга (пр), К427</t>
   </si>
 </sst>
 </file>
@@ -471,7 +540,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,12 +559,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -739,6 +814,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1096,6 +1184,17 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1224,7 +1323,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1264,16 +1363,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1301,9 +1403,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1311,23 +1415,24 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1335,23 +1440,30 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1360,18 +1472,32 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1381,25 +1507,25 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1417,40 +1543,40 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1459,12 +1585,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1474,27 +1600,27 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1504,9 +1630,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1519,44 +1645,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1569,75 +1695,72 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1645,38 +1768,38 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1684,38 +1807,38 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1723,8 +1846,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1732,11 +1855,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1744,27 +1867,30 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2096,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2105,10 +2231,11 @@
     <col min="4" max="4" width="16.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2116,15 +2243,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2132,41 +2259,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="127" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="150" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
       <c r="F4" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="48"/>
       <c r="E6" s="7">
         <v>1</v>
       </c>
@@ -2174,46 +2301,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="12" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="45"/>
+        <v>28</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="49"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="128"/>
+        <v>34</v>
+      </c>
+      <c r="C9" s="151" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="151"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -2224,355 +2351,425 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="23">
         <v>2</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="126"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="24"/>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="106"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="129"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="24"/>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="109" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="132" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="24"/>
+    </row>
+    <row r="14" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
         <v>5</v>
       </c>
-      <c r="C14" s="112" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="C14" s="135" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="81" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="24"/>
+    </row>
+    <row r="15" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="30">
         <v>1</v>
       </c>
-      <c r="C15" s="91" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="92"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="114" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="115"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="71" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>2</v>
       </c>
-      <c r="C16" s="109" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="23"/>
-    </row>
-    <row r="17" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="24"/>
+    </row>
+    <row r="17" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="106" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="24"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="28">
+        <v>4</v>
+      </c>
+      <c r="C18" s="152"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="154"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="24"/>
+    </row>
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="30">
+        <v>3</v>
+      </c>
+      <c r="C19" s="111" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="24"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
+        <v>4</v>
+      </c>
+      <c r="C20" s="147" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="148"/>
+      <c r="E20" s="148"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="76" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" s="24"/>
+    </row>
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
+        <v>5</v>
+      </c>
+      <c r="C21" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="76" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="24"/>
+    </row>
+    <row r="22" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="28">
+        <v>6</v>
+      </c>
+      <c r="C22" s="100" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" s="24"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="30">
+        <v>1</v>
+      </c>
+      <c r="C23" s="125"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="24"/>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
+        <v>2</v>
+      </c>
+      <c r="C24" s="109"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="107" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="108"/>
+      <c r="G24" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="24"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
+        <v>3</v>
+      </c>
+      <c r="C25" s="106" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="24"/>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="32"/>
+      <c r="B26" s="28">
+        <v>4</v>
+      </c>
+      <c r="C26" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="24"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="30">
+        <v>1</v>
+      </c>
+      <c r="C27" s="103" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="24"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="23">
+        <v>2</v>
+      </c>
+      <c r="C28" s="94" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="95"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="24"/>
+    </row>
+    <row r="29" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="26">
+        <v>3</v>
+      </c>
+      <c r="C29" s="141" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="142"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="24"/>
+    </row>
+    <row r="30" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="28">
+        <v>4</v>
+      </c>
+      <c r="C30" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="30"/>
-      <c r="B18" s="27">
-        <v>4</v>
-      </c>
-      <c r="C18" s="129"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="23"/>
-    </row>
-    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="29">
-        <v>3</v>
-      </c>
-      <c r="C19" s="88" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="23"/>
-    </row>
-    <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
-        <v>4</v>
-      </c>
-      <c r="C20" s="124" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
-        <v>5</v>
-      </c>
-      <c r="C21" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="23"/>
-    </row>
-    <row r="22" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="27">
-        <v>6</v>
-      </c>
-      <c r="C22" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="23"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="81" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="24"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="23">
         <v>1</v>
       </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="C31" s="97"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="24"/>
+    </row>
+    <row r="32" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38">
         <v>2</v>
       </c>
-      <c r="C24" s="86"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="84" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="85"/>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="25" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
-        <v>3</v>
-      </c>
-      <c r="C25" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="23"/>
-    </row>
-    <row r="26" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27">
-        <v>4</v>
-      </c>
-      <c r="C26" s="99" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="29">
-        <v>1</v>
-      </c>
-      <c r="C27" s="80" t="s">
+      <c r="C32" s="144"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="146"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="24"/>
+    </row>
+    <row r="33" spans="1:8" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="24"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="42"/>
+      <c r="B34" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="138" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="24"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="44"/>
+      <c r="B35" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="24"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="64"/>
+      <c r="B36" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="77" t="s">
+        <v>56</v>
+      </c>
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="46"/>
+      <c r="B37" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="22">
-        <v>2</v>
-      </c>
-      <c r="C28" s="71" t="s">
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="23"/>
-    </row>
-    <row r="29" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
-        <v>3</v>
-      </c>
-      <c r="C29" s="118" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="23"/>
-    </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="27">
-        <v>4</v>
-      </c>
-      <c r="C30" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="23"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="22">
-        <v>1</v>
-      </c>
-      <c r="C31" s="74"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="23"/>
-    </row>
-    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="34"/>
-      <c r="B32" s="35">
-        <v>2</v>
-      </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="123"/>
-      <c r="G32" s="23"/>
-    </row>
-    <row r="33" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="36"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="68"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="23"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="115" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="23"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="40"/>
-      <c r="B35" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="23"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" s="55"/>
-      <c r="B36" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="23"/>
-    </row>
-    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="42"/>
-      <c r="B37" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="95" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="23"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H37" s="24"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
@@ -2580,7 +2777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
@@ -2659,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2668,10 +2865,11 @@
     <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2679,15 +2877,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2695,41 +2893,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="127" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="150" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
       <c r="F4" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="48"/>
       <c r="E6" s="7">
         <v>2</v>
       </c>
@@ -2737,46 +2935,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="12" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="45"/>
+        <v>28</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="49"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="128"/>
+        <v>34</v>
+      </c>
+      <c r="C9" s="151" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="151"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -2787,332 +2985,391 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="138" t="s">
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="161" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="163"/>
+      <c r="G11" s="63"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
+        <v>4</v>
+      </c>
+      <c r="C12" s="129"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="69"/>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="50"/>
+      <c r="B13" s="38">
+        <v>5</v>
+      </c>
+      <c r="C13" s="199" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="185"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="78" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
+        <v>6</v>
+      </c>
+      <c r="C14" s="158"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="68"/>
+    </row>
+    <row r="15" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="30">
+        <v>1</v>
+      </c>
+      <c r="C15" s="155"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="157"/>
+      <c r="G15" s="71"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
+        <v>2</v>
+      </c>
+      <c r="C16" s="183"/>
+      <c r="D16" s="184"/>
+      <c r="E16" s="185" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="186"/>
+      <c r="G16" s="72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
+        <v>3</v>
+      </c>
+      <c r="C17" s="167"/>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="69"/>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="50"/>
+      <c r="B18" s="38">
+        <v>4</v>
+      </c>
+      <c r="C18" s="170"/>
+      <c r="D18" s="171"/>
+      <c r="E18" s="171"/>
+      <c r="F18" s="172"/>
+      <c r="G18" s="68"/>
+    </row>
+    <row r="19" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="30">
+        <v>1</v>
+      </c>
+      <c r="C19" s="164" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="71" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
+        <v>2</v>
+      </c>
+      <c r="C20" s="173" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="174"/>
+      <c r="E20" s="174"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="74" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
+        <v>3</v>
+      </c>
+      <c r="C21" s="147" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="148"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="149"/>
+      <c r="G21" s="72" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="28">
+        <v>4</v>
+      </c>
+      <c r="C22" s="170"/>
+      <c r="D22" s="171"/>
+      <c r="E22" s="171"/>
+      <c r="F22" s="172"/>
+      <c r="G22" s="68"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="161" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="162"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="163"/>
+      <c r="G23" s="75"/>
+    </row>
+    <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
+        <v>4</v>
+      </c>
+      <c r="C24" s="173"/>
+      <c r="D24" s="174"/>
+      <c r="E24" s="174"/>
+      <c r="F24" s="175"/>
+      <c r="G24" s="74"/>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="50"/>
+      <c r="B25" s="38">
+        <v>5</v>
+      </c>
+      <c r="C25" s="179"/>
+      <c r="D25" s="180"/>
+      <c r="E25" s="180"/>
+      <c r="F25" s="181"/>
+      <c r="G25" s="77"/>
+    </row>
+    <row r="26" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="32"/>
+      <c r="B26" s="28">
+        <v>6</v>
+      </c>
+      <c r="C26" s="193"/>
+      <c r="D26" s="194"/>
+      <c r="E26" s="194"/>
+      <c r="F26" s="195"/>
+      <c r="G26" s="33"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="30">
+        <v>3</v>
+      </c>
+      <c r="C27" s="196"/>
+      <c r="D27" s="197"/>
+      <c r="E27" s="197"/>
+      <c r="F27" s="198"/>
+      <c r="G27" s="63"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="26">
+        <v>4</v>
+      </c>
+      <c r="C28" s="179" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="180"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="74" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="26">
+        <v>5</v>
+      </c>
+      <c r="C29" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="28">
+        <v>6</v>
+      </c>
+      <c r="C30" s="176" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="177"/>
+      <c r="E30" s="177"/>
+      <c r="F30" s="178"/>
+      <c r="G30" s="81" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="30">
+        <v>1</v>
+      </c>
+      <c r="C31" s="111" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="75" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="52"/>
+      <c r="B32" s="26">
+        <v>2</v>
+      </c>
+      <c r="C32" s="173" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="174"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="175"/>
+      <c r="G32" s="74" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="53"/>
+      <c r="B33" s="28">
+        <v>3</v>
+      </c>
+      <c r="C33" s="118" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="79" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="54"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="187"/>
+      <c r="D34" s="188"/>
+      <c r="E34" s="188"/>
+      <c r="F34" s="189"/>
+      <c r="G34" s="56"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="57"/>
+      <c r="B35" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="140"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
-        <v>4</v>
-      </c>
-      <c r="C12" s="106"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="108"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="46"/>
-      <c r="B13" s="35">
-        <v>5</v>
-      </c>
-      <c r="C13" s="176" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="162"/>
-      <c r="E13" s="177"/>
-      <c r="F13" s="178"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
-        <v>6</v>
-      </c>
-      <c r="C14" s="135"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="137"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="29">
-        <v>1</v>
-      </c>
-      <c r="C15" s="132"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="134"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
-        <v>2</v>
-      </c>
-      <c r="C16" s="160"/>
-      <c r="D16" s="161"/>
-      <c r="E16" s="162" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="163"/>
-    </row>
-    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
-        <v>3</v>
-      </c>
-      <c r="C17" s="144"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="146"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="46"/>
-      <c r="B18" s="35">
-        <v>4</v>
-      </c>
-      <c r="C18" s="147"/>
-      <c r="D18" s="148"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="149"/>
-    </row>
-    <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="29">
-        <v>1</v>
-      </c>
-      <c r="C19" s="141" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="143"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
-        <v>2</v>
-      </c>
-      <c r="C20" s="150" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="151"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="152"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
-        <v>3</v>
-      </c>
-      <c r="C21" s="124" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="125"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="126"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="27">
-        <v>4</v>
-      </c>
-      <c r="C22" s="147"/>
-      <c r="D22" s="148"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="149"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="138" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="139"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="140"/>
-    </row>
-    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
-        <v>4</v>
-      </c>
-      <c r="C24" s="150"/>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="152"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="46"/>
-      <c r="B25" s="35">
-        <v>5</v>
-      </c>
-      <c r="C25" s="156"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
-      <c r="F25" s="158"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27">
-        <v>6</v>
-      </c>
-      <c r="C26" s="170"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="172"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="29">
-        <v>3</v>
-      </c>
-      <c r="C27" s="173"/>
-      <c r="D27" s="174"/>
-      <c r="E27" s="174"/>
-      <c r="F27" s="175"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="25">
-        <v>4</v>
-      </c>
-      <c r="C28" s="156" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" s="157"/>
-      <c r="E28" s="157"/>
-      <c r="F28" s="158"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
-        <v>5</v>
-      </c>
-      <c r="C29" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="27">
-        <v>6</v>
-      </c>
-      <c r="C30" s="153" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="154"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="155"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="29">
-        <v>1</v>
-      </c>
-      <c r="C31" s="88" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="90"/>
-    </row>
-    <row r="32" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
-      <c r="B32" s="25">
-        <v>2</v>
-      </c>
-      <c r="C32" s="150" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="151"/>
-      <c r="E32" s="151"/>
-      <c r="F32" s="152"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="49"/>
-      <c r="B33" s="27">
-        <v>3</v>
-      </c>
-      <c r="C33" s="95" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="97"/>
-    </row>
-    <row r="34" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="50"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="164"/>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="166"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="52"/>
-      <c r="B35" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="115" t="s">
+      <c r="D35" s="139"/>
+      <c r="E35" s="139"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="71" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="37"/>
+      <c r="B36" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="82" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="117"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="34"/>
-      <c r="B36" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="61"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="53"/>
-      <c r="B37" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="167" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="169"/>
-    </row>
-    <row r="38" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="58"/>
-      <c r="C38" s="159" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="159"/>
-      <c r="E38" s="159"/>
-      <c r="F38" s="159"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="58"/>
+      <c r="B37" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="190" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="191"/>
+      <c r="E37" s="191"/>
+      <c r="F37" s="192"/>
+      <c r="G37" s="81" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="67"/>
+      <c r="C38" s="182" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="182"/>
+      <c r="E38" s="182"/>
+      <c r="F38" s="182"/>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
@@ -3120,7 +3377,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
@@ -3214,7 +3471,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3223,10 +3480,11 @@
     <col min="4" max="4" width="16.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3234,15 +3492,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3250,41 +3508,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="127" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="150" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
       <c r="F4" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="48"/>
       <c r="E6" s="7">
         <v>3</v>
       </c>
@@ -3292,46 +3550,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="45"/>
+        <v>28</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="49"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="128"/>
+        <v>34</v>
+      </c>
+      <c r="C9" s="151" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="151"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -3342,304 +3600,361 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="23">
         <v>3</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="126"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="63"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>4</v>
       </c>
-      <c r="C12" s="71" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="73"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="94" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="76" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>5</v>
       </c>
-      <c r="C13" s="118" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="119"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="120"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="141" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="76" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
         <v>6</v>
       </c>
-      <c r="C14" s="201" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="203"/>
-    </row>
-    <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="C14" s="224" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="226"/>
+      <c r="G14" s="81" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="30">
         <v>1</v>
       </c>
-      <c r="C15" s="115" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="138" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="74" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>2</v>
       </c>
-      <c r="C16" s="83" t="s">
+      <c r="C16" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="72" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
+        <v>3</v>
+      </c>
+      <c r="C17" s="183"/>
+      <c r="D17" s="184"/>
+      <c r="E17" s="184"/>
+      <c r="F17" s="227"/>
+      <c r="G17" s="72"/>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="28">
+        <v>4</v>
+      </c>
+      <c r="C18" s="221"/>
+      <c r="D18" s="222"/>
+      <c r="E18" s="222"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="81"/>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="30">
+        <v>1</v>
+      </c>
+      <c r="C19" s="228" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="229"/>
+      <c r="E19" s="229"/>
+      <c r="F19" s="230"/>
+      <c r="G19" s="71" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
+        <v>2</v>
+      </c>
+      <c r="C20" s="147" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="148"/>
+      <c r="E20" s="148"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="72" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
+        <v>3</v>
+      </c>
+      <c r="C21" s="208" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="209"/>
+      <c r="E21" s="209"/>
+      <c r="F21" s="210"/>
+      <c r="G21" s="72" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="28">
+        <v>4</v>
+      </c>
+      <c r="C22" s="231"/>
+      <c r="D22" s="232"/>
+      <c r="E22" s="215" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="216"/>
+      <c r="G22" s="72" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="30">
+        <v>1</v>
+      </c>
+      <c r="C23" s="114" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="214"/>
+      <c r="G23" s="80" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
+        <v>2</v>
+      </c>
+      <c r="C24" s="106" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
+        <v>3</v>
+      </c>
+      <c r="C25" s="199" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="185"/>
+      <c r="E25" s="185"/>
+      <c r="F25" s="186"/>
+      <c r="G25" s="76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="32"/>
+      <c r="B26" s="28">
+        <v>4</v>
+      </c>
+      <c r="C26" s="217" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="218"/>
+      <c r="E26" s="219"/>
+      <c r="F26" s="220"/>
+      <c r="G26" s="76" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="211" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="212"/>
+      <c r="E27" s="212"/>
+      <c r="F27" s="213"/>
+      <c r="G27" s="63"/>
+    </row>
+    <row r="28" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="26">
+        <v>4</v>
+      </c>
+      <c r="C28" s="147" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="85"/>
-    </row>
-    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="D28" s="148"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="149"/>
+      <c r="G28" s="76" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="26">
+        <v>5</v>
+      </c>
+      <c r="C29" s="173" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="175"/>
+      <c r="G29" s="76" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="28">
+        <v>6</v>
+      </c>
+      <c r="C30" s="205"/>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="207"/>
+      <c r="G30" s="68"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="23">
+        <v>2</v>
+      </c>
+      <c r="C31" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="31"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="52"/>
+      <c r="B32" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="160"/>
-      <c r="D17" s="161"/>
-      <c r="E17" s="161"/>
-      <c r="F17" s="204"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="30"/>
-      <c r="B18" s="27">
+      <c r="C32" s="202"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="204"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="52"/>
+      <c r="B33" s="26">
         <v>4</v>
       </c>
-      <c r="C18" s="198"/>
-      <c r="D18" s="199"/>
-      <c r="E18" s="199"/>
-      <c r="F18" s="200"/>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="29">
-        <v>1</v>
-      </c>
-      <c r="C19" s="205" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="206"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="207"/>
-    </row>
-    <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
-        <v>2</v>
-      </c>
-      <c r="C20" s="124" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="126"/>
-    </row>
-    <row r="21" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
-        <v>3</v>
-      </c>
-      <c r="C21" s="185" t="s">
+      <c r="C33" s="202"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="31"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="58"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="144"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="33"/>
+    </row>
+    <row r="35" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="186"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="187"/>
-    </row>
-    <row r="22" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="27">
-        <v>4</v>
-      </c>
-      <c r="C22" s="208"/>
-      <c r="D22" s="209"/>
-      <c r="E22" s="192" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="193"/>
-    </row>
-    <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="29">
-        <v>1</v>
-      </c>
-      <c r="C23" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="191"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
-        <v>2</v>
-      </c>
-      <c r="C24" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="85"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
-        <v>3</v>
-      </c>
-      <c r="C25" s="176" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="162"/>
-      <c r="E25" s="162"/>
-      <c r="F25" s="163"/>
-    </row>
-    <row r="26" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27">
-        <v>4</v>
-      </c>
-      <c r="C26" s="194" t="s">
+      <c r="B35" s="67"/>
+      <c r="C35" s="182" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="195"/>
-      <c r="E26" s="196"/>
-      <c r="F26" s="197"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="188" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="189"/>
-      <c r="E27" s="189"/>
-      <c r="F27" s="190"/>
-    </row>
-    <row r="28" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="25">
-        <v>4</v>
-      </c>
-      <c r="C28" s="124" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="125"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="126"/>
-    </row>
-    <row r="29" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
-        <v>5</v>
-      </c>
-      <c r="C29" s="150" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="152"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="27">
-        <v>6</v>
-      </c>
-      <c r="C30" s="182"/>
-      <c r="D30" s="183"/>
-      <c r="E30" s="183"/>
-      <c r="F30" s="184"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="22">
-        <v>2</v>
-      </c>
-      <c r="C31" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="61"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
-      <c r="B32" s="25">
-        <v>3</v>
-      </c>
-      <c r="C32" s="179"/>
-      <c r="D32" s="180"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="181"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
-      <c r="B33" s="25">
-        <v>4</v>
-      </c>
-      <c r="C33" s="179"/>
-      <c r="D33" s="180"/>
-      <c r="E33" s="180"/>
-      <c r="F33" s="181"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="53"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="121"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="123"/>
-    </row>
-    <row r="35" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="159" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="159"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D35" s="182"/>
+      <c r="E35" s="182"/>
+      <c r="F35" s="182"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
@@ -3647,7 +3962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
@@ -3738,7 +4053,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3747,10 +4062,11 @@
     <col min="4" max="4" width="19" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3758,15 +4074,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3774,41 +4090,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="127" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="150" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
       <c r="F4" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
+      <c r="C6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="48"/>
       <c r="E6" s="7">
         <v>4</v>
       </c>
@@ -3816,342 +4132,394 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="45"/>
+        <v>28</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="49"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="128"/>
+        <v>34</v>
+      </c>
+      <c r="C9" s="151" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="151"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="226" t="s">
+      <c r="C10" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="227"/>
-      <c r="E10" s="227"/>
-      <c r="F10" s="228"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="D10" s="250"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="23">
         <v>2</v>
       </c>
-      <c r="C11" s="225" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="140"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="248" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="163"/>
+      <c r="G11" s="75" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="156" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
-      <c r="F12" s="158"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="179" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="180"/>
+      <c r="E12" s="180"/>
+      <c r="F12" s="181"/>
+      <c r="G12" s="74" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>7</v>
       </c>
-      <c r="C13" s="210"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="211"/>
-      <c r="F13" s="212"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="233"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="74"/>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
         <v>8</v>
       </c>
-      <c r="C14" s="216"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="218"/>
-    </row>
-    <row r="15" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="C14" s="239"/>
+      <c r="D14" s="240"/>
+      <c r="E14" s="240"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="79"/>
+    </row>
+    <row r="15" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="30">
         <v>3</v>
       </c>
-      <c r="C15" s="91" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="92"/>
-      <c r="E15" s="223"/>
-      <c r="F15" s="224"/>
-    </row>
-    <row r="16" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="114" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="115"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="247"/>
+      <c r="G15" s="80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>4</v>
       </c>
-      <c r="C16" s="124"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="125" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="126"/>
-    </row>
-    <row r="17" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="147"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="149"/>
+      <c r="G16" s="76" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>5</v>
       </c>
-      <c r="C17" s="229"/>
-      <c r="D17" s="230"/>
-      <c r="E17" s="230"/>
-      <c r="F17" s="231"/>
-    </row>
-    <row r="18" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="30"/>
-      <c r="B18" s="27">
+      <c r="C17" s="252"/>
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="69"/>
+    </row>
+    <row r="18" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="28">
         <v>6</v>
       </c>
-      <c r="C18" s="170"/>
-      <c r="D18" s="171"/>
-      <c r="E18" s="171"/>
-      <c r="F18" s="172"/>
-    </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="29">
+      <c r="C18" s="193"/>
+      <c r="D18" s="194"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="195"/>
+      <c r="G18" s="68"/>
+    </row>
+    <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="30">
         <v>2</v>
       </c>
-      <c r="C19" s="88" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="90"/>
-    </row>
-    <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="C19" s="111" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
         <v>3</v>
       </c>
-      <c r="C20" s="150" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="151"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="152"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="C20" s="173" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="174"/>
+      <c r="E20" s="174"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="74" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <v>4</v>
       </c>
-      <c r="C21" s="210"/>
-      <c r="D21" s="211"/>
-      <c r="E21" s="211"/>
-      <c r="F21" s="212"/>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="27">
+      <c r="C21" s="233"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="31"/>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="28">
         <v>5</v>
       </c>
-      <c r="C22" s="216"/>
-      <c r="D22" s="217"/>
-      <c r="E22" s="217"/>
-      <c r="F22" s="218"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="C22" s="239"/>
+      <c r="D22" s="240"/>
+      <c r="E22" s="240"/>
+      <c r="F22" s="241"/>
+      <c r="G22" s="33"/>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="30">
         <v>5</v>
       </c>
-      <c r="C23" s="115" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="116"/>
-      <c r="E23" s="116"/>
-      <c r="F23" s="117"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="C23" s="138" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="139"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="75" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <v>6</v>
       </c>
-      <c r="C24" s="156" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
-      <c r="F24" s="158"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
+      <c r="C24" s="179" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="180"/>
+      <c r="E24" s="180"/>
+      <c r="F24" s="181"/>
+      <c r="G24" s="74" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
         <v>7</v>
       </c>
-      <c r="C25" s="156" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
-      <c r="F25" s="158"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27">
+      <c r="C25" s="179" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="180"/>
+      <c r="E25" s="180"/>
+      <c r="F25" s="181"/>
+      <c r="G25" s="74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="32"/>
+      <c r="B26" s="28">
         <v>8</v>
       </c>
-      <c r="C26" s="220" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" s="221"/>
-      <c r="E26" s="221"/>
-      <c r="F26" s="222"/>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="29">
+      <c r="C26" s="243" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="79" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="30">
         <v>1</v>
       </c>
-      <c r="C27" s="150" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="152"/>
-    </row>
-    <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="25">
+      <c r="C27" s="173" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="174"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="175"/>
+      <c r="G27" s="74" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="26">
         <v>2</v>
       </c>
-      <c r="C28" s="156" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="157"/>
-      <c r="E28" s="157"/>
-      <c r="F28" s="158"/>
-    </row>
-    <row r="29" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
+      <c r="C28" s="179" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="180"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="74" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="26">
         <v>3</v>
       </c>
-      <c r="C29" s="219"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="177"/>
-      <c r="F29" s="178"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="27">
+      <c r="C29" s="242"/>
+      <c r="D29" s="200"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="201"/>
+      <c r="G29" s="74"/>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="28">
         <v>4</v>
       </c>
-      <c r="C30" s="213"/>
-      <c r="D30" s="214"/>
-      <c r="E30" s="214"/>
-      <c r="F30" s="215"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="22">
+      <c r="C30" s="236"/>
+      <c r="D30" s="237"/>
+      <c r="E30" s="237"/>
+      <c r="F30" s="238"/>
+      <c r="G30" s="79"/>
+    </row>
+    <row r="31" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="23">
         <v>1</v>
       </c>
-      <c r="C31" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="61"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="48"/>
-      <c r="B32" s="25">
+      <c r="C31" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="59"/>
+    </row>
+    <row r="32" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="52"/>
+      <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="210"/>
-      <c r="D32" s="211"/>
-      <c r="E32" s="211"/>
-      <c r="F32" s="212"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
-      <c r="B33" s="25">
+      <c r="C32" s="233"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="234"/>
+      <c r="F32" s="235"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="52"/>
+      <c r="B33" s="26">
         <v>3</v>
       </c>
-      <c r="C33" s="210"/>
-      <c r="D33" s="211"/>
-      <c r="E33" s="211"/>
-      <c r="F33" s="212"/>
-    </row>
-    <row r="34" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="53"/>
-      <c r="B34" s="54">
+      <c r="C33" s="233"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="31"/>
+    </row>
+    <row r="34" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="58"/>
+      <c r="B34" s="60">
         <v>4</v>
       </c>
-      <c r="C34" s="121"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="123"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="144"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="33"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
@@ -4159,7 +4527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
